--- a/XLibur.Tests/Resource/Examples/Tables/ResizingTables.xlsx
+++ b/XLibur.Tests/Resource/Examples/Tables/ResizingTables.xlsx
@@ -509,8 +509,8 @@
   <x:cols>
     <x:col min="1" max="1" width="9.140625" style="0" customWidth="1"/>
     <x:col min="2" max="2" width="14.139196" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="11.853482" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="11.282054" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="11.996339" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="11.424911" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="9.710625" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
@@ -697,8 +697,8 @@
   <x:cols>
     <x:col min="1" max="1" width="9.140625" style="0" customWidth="1"/>
     <x:col min="2" max="2" width="14.139196" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="11.853482" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="11.282054" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="11.996339" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="11.424911" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="9.710625" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
@@ -892,8 +892,8 @@
   <x:cols>
     <x:col min="1" max="1" width="11.282054" style="0" customWidth="1"/>
     <x:col min="2" max="2" width="14.139196" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="11.853482" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="11.282054" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="11.996339" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="11.424911" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="9.710625" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
@@ -1090,8 +1090,9 @@
   <x:cols>
     <x:col min="1" max="1" width="9.140625" style="0" customWidth="1"/>
     <x:col min="2" max="2" width="14.139196" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="11.853482" style="0" customWidth="1"/>
-    <x:col min="4" max="5" width="11.282054" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="11.996339" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="11.424911" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="11.282054" style="0" customWidth="1"/>
     <x:col min="6" max="6" width="9.710625" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>

--- a/XLibur.Tests/Resource/Examples/Tables/ResizingTables.xlsx
+++ b/XLibur.Tests/Resource/Examples/Tables/ResizingTables.xlsx
@@ -860,8 +860,9 @@
       <x:c r="D13" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="E13" s="0">
+      <x:c r="E13" s="0" t="e">
         <x:f>SUBTOTAL(109,[Integer])</x:f>
+        <x:v>#REF!</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1058,8 +1059,9 @@
       <x:c r="D13" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="E13" s="0">
+      <x:c r="E13" s="0" t="e">
         <x:f>SUBTOTAL(109,[Integer])</x:f>
+        <x:v>#REF!</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
